--- a/sharing_consent_forms/023_volunteer_recognition_video_consent_form--sharing_consent_forms.xlsx
+++ b/sharing_consent_forms/023_volunteer_recognition_video_consent_form--sharing_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent</t>
+          <t>Volunteer Recognition Video Consent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,36 +548,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>i_agree_to_al</t>
+          <t>Do you agree to the use of your recorded video in the recognition program?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_2</t>
+          <t>volunteer_recognition_video_consent_form_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_2</t>
+          <t>Role in the Recognition Program</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_3</t>
+          <t>volunteer_recognition_video_consent_form_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent</t>
+          <t>Organization/Agency</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_4</t>
+          <t>volunteer_recognition_video_consent_form_page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>Start Date of Volunteering</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_4</t>
+          <t>volunteer_recognition_video_consent_form_page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>Time of Day Volunteered</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,43 +653,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_5</t>
+          <t>volunteer_recognition_video_consent_form_page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_6</t>
+          <t>volunteer_recognition_video_consent_form_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Brief Description</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of your volunteer work (up to 200 characters)</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,18 +708,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_7</t>
+          <t>volunteer_recognition_video_consent_form_page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Hours Volunteered in Past 12 Months</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,64 +731,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_8</t>
+          <t>volunteer_recognition_video_consent_form_page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent</t>
+          <t>Hours Volunteered for this Event</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>volunteer_recognition_video_consent_form_page_9</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>volunteer_recognition_video_consent</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>volunteer_recognition_video_consent_form_page_10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>volunteer_recognition_video_consent</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,12 +757,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +790,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -849,46 +807,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_2_choices</t>
+          <t>volunteer_recognition_video_consent_form_page_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>volunteer_recognition_video_consent_form_page_2_choices</t>
+          <t>volunteer_recognition_video_consent_form_page_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>Team Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>volunteer_recognition_video_consent_form_page_3_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
